--- a/workshop_registration_form_templates/026_innovation_in_preservation_forum_registration_form--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/026_innovation_in_preservation_forum_registration_form--workshop_registration_form_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>General Details</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>How can we contact you?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone_info</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -574,17 +574,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Do you have any comments about this form?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -620,17 +620,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>contact_method</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>How can we reach you?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>name_2</t>
+          <t>phone_verification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Is this your phone number?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,200 +671,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>phone_2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>comments_2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>form_submission</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Form Submission</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>comments_3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>general_details_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>general_details</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>name_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>email_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>phone_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
